--- a/templates/금거래소_데이터이관_템플릿.xlsx
+++ b/templates/금거래소_데이터이관_템플릿.xlsx
@@ -682,7 +682,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>직원ID: 그룹은 M(Manager), S(Sub Manager), U(User) 중 하나. 임시비밀번호로 처음 로그인하면 새 비밀번호를 설정해야 합니다. Administrator(A) 계정은 올리지 않습니다.</t>
+          <t>직원ID: 그룹은 M(Manager), S(Sub Manager), U(User) 중 하나. 임시비밀번호로 처음 로그인하면 새 비밀번호를 설정해야 합니다. Administrator(A) 계정은 올리지 않습니다. 아이디는 같은 매장 안에서만 중복되지 않으면 되며, 다른 매장과 같아도 됩니다.</t>
         </is>
       </c>
     </row>
